--- a/Data/collapsed database manual cases/mexico_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/mexico_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2628327D-00F4-7340-A6F2-D8E54D53C116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBD86D2-5FAA-DF42-AC7A-ED44B08E3C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9702" uniqueCount="1980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9707" uniqueCount="1981">
   <si>
     <t>uniqueid</t>
   </si>
@@ -5956,13 +5956,16 @@
     <t>https://www.ieem.org.mx/consejo_general/cg/2018/acu_18/a104_18.pdf</t>
   </si>
   <si>
-    <t>PVR</t>
-  </si>
-  <si>
     <t>https://www.ieem.org.mx/consejo_general/cg/2021/AC_21/a095_21.pdf</t>
   </si>
   <si>
     <t>https://www.ieem.org.mx/consejo_general/cg/2021/AC_21/a096_21.pdf</t>
+  </si>
+  <si>
+    <t>JOSE VICENTE ESTRADA PALACIOS</t>
+  </si>
+  <si>
+    <t>VR</t>
   </si>
 </sst>
 </file>
@@ -6442,7 +6445,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S1001"/>
+  <dimension ref="A1:S1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -46713,7 +46716,7 @@
         <v>21</v>
       </c>
       <c r="I902" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="903" spans="1:9" x14ac:dyDescent="0.2">
@@ -46733,7 +46736,7 @@
         <v>21</v>
       </c>
       <c r="I903" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.2">
@@ -46753,7 +46756,7 @@
         <v>21</v>
       </c>
       <c r="I904" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.2">
@@ -46793,7 +46796,7 @@
         <v>84</v>
       </c>
       <c r="I906" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.2">
@@ -46813,7 +46816,7 @@
         <v>21</v>
       </c>
       <c r="I907" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.2">
@@ -46833,7 +46836,7 @@
         <v>21</v>
       </c>
       <c r="I908" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="909" spans="1:9" x14ac:dyDescent="0.2">
@@ -46853,7 +46856,7 @@
         <v>21</v>
       </c>
       <c r="I909" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.2">
@@ -46913,7 +46916,7 @@
         <v>21</v>
       </c>
       <c r="I912" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="913" spans="1:9" x14ac:dyDescent="0.2">
@@ -46933,7 +46936,7 @@
         <v>24</v>
       </c>
       <c r="I913" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.2">
@@ -46953,7 +46956,7 @@
         <v>21</v>
       </c>
       <c r="I914" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.2">
@@ -46993,7 +46996,7 @@
         <v>21</v>
       </c>
       <c r="I916" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="917" spans="1:9" x14ac:dyDescent="0.2">
@@ -47013,7 +47016,7 @@
         <v>21</v>
       </c>
       <c r="I917" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="918" spans="1:9" x14ac:dyDescent="0.2">
@@ -47053,7 +47056,7 @@
         <v>24</v>
       </c>
       <c r="I919" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="920" spans="1:9" x14ac:dyDescent="0.2">
@@ -47073,7 +47076,7 @@
         <v>21</v>
       </c>
       <c r="I920" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="921" spans="1:9" x14ac:dyDescent="0.2">
@@ -47093,7 +47096,7 @@
         <v>84</v>
       </c>
       <c r="I921" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.2">
@@ -47113,7 +47116,7 @@
         <v>84</v>
       </c>
       <c r="I922" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.2">
@@ -47133,7 +47136,7 @@
         <v>24</v>
       </c>
       <c r="I923" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.2">
@@ -47153,7 +47156,7 @@
         <v>1372</v>
       </c>
       <c r="I924" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.2">
@@ -47213,7 +47216,7 @@
         <v>1372</v>
       </c>
       <c r="I927" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="928" spans="1:9" x14ac:dyDescent="0.2">
@@ -47253,7 +47256,7 @@
         <v>1372</v>
       </c>
       <c r="I929" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="930" spans="1:9" x14ac:dyDescent="0.2">
@@ -47313,7 +47316,7 @@
         <v>1372</v>
       </c>
       <c r="I932" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="933" spans="1:9" x14ac:dyDescent="0.2">
@@ -47333,7 +47336,7 @@
         <v>1372</v>
       </c>
       <c r="I933" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="934" spans="1:9" x14ac:dyDescent="0.2">
@@ -47373,7 +47376,7 @@
         <v>1372</v>
       </c>
       <c r="I935" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="936" spans="1:9" x14ac:dyDescent="0.2">
@@ -47433,7 +47436,7 @@
         <v>1372</v>
       </c>
       <c r="I938" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="939" spans="1:9" x14ac:dyDescent="0.2">
@@ -47453,7 +47456,7 @@
         <v>1372</v>
       </c>
       <c r="I939" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="940" spans="1:9" x14ac:dyDescent="0.2">
@@ -47473,7 +47476,7 @@
         <v>1372</v>
       </c>
       <c r="I940" s="18" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.2">
@@ -47513,7 +47516,7 @@
         <v>113</v>
       </c>
       <c r="I942" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="943" spans="1:9" x14ac:dyDescent="0.2">
@@ -47533,7 +47536,7 @@
         <v>113</v>
       </c>
       <c r="I943" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="944" spans="1:9" x14ac:dyDescent="0.2">
@@ -47613,7 +47616,7 @@
         <v>1372</v>
       </c>
       <c r="I947" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="948" spans="1:9" x14ac:dyDescent="0.2">
@@ -48438,7 +48441,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="993" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993">
         <v>15104</v>
       </c>
@@ -48458,7 +48461,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="994" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A994">
         <v>15106</v>
       </c>
@@ -48475,7 +48478,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="995" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995">
         <v>15109</v>
       </c>
@@ -48495,7 +48498,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="996" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996">
         <v>15118</v>
       </c>
@@ -48515,7 +48518,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="997" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997">
         <v>15119</v>
       </c>
@@ -48532,7 +48535,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="998" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998">
         <v>15120</v>
       </c>
@@ -48549,7 +48552,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="999" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A999">
         <v>15121</v>
       </c>
@@ -48569,7 +48572,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="1000" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1000">
         <v>15122</v>
       </c>
@@ -48586,7 +48589,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="1001" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1001">
         <v>15015</v>
       </c>
@@ -48600,7 +48603,30 @@
         <v>1889</v>
       </c>
       <c r="H1001" t="s">
-        <v>1977</v>
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1002">
+        <v>15055</v>
+      </c>
+      <c r="B1002">
+        <v>2021</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>1888</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H1002" t="s">
+        <v>1980</v>
+      </c>
+      <c r="J1002" t="s">
+        <v>1980</v>
+      </c>
+      <c r="K1002" t="s">
+        <v>1979</v>
       </c>
     </row>
   </sheetData>
